--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:21</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,7 +558,7 @@
         <v>37.52</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45.59</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="7">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:48</t>
+    <t xml:space="preserve">2026-10-05 04:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>0.38</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>77.04</v>
+        <v>77.05</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>76.67</v>
@@ -558,7 +558,7 @@
         <v>37.52</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45.58</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="7">
